--- a/artfynd/A 49000-2025 artfynd.xlsx
+++ b/artfynd/A 49000-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129574107</v>
       </c>
       <c r="B2" t="n">
-        <v>56920</v>
+        <v>56925</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49000-2025 artfynd.xlsx
+++ b/artfynd/A 49000-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129574107</v>
       </c>
       <c r="B2" t="n">
-        <v>56925</v>
+        <v>56926</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49000-2025 artfynd.xlsx
+++ b/artfynd/A 49000-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129574107</v>
       </c>
       <c r="B2" t="n">
-        <v>56926</v>
+        <v>56927</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49000-2025 artfynd.xlsx
+++ b/artfynd/A 49000-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129574107</v>
       </c>
       <c r="B2" t="n">
-        <v>56927</v>
+        <v>56930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 49000-2025 artfynd.xlsx
+++ b/artfynd/A 49000-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,6 +786,1829 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>130134265</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79220</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>750588</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7111098</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130134356</v>
+      </c>
+      <c r="B4" t="n">
+        <v>93061</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>750732</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7111314</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Daniel Lussetti</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130134267</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98971</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>750666</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7111136</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>130134262</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79220</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>750629</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7111290</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>130134353</v>
+      </c>
+      <c r="B7" t="n">
+        <v>93061</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>750686</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7111300</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Daniel Lussetti</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>130134261</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79220</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>750701</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7111370</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>130134269</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79220</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>750667</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7111133</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130134260</v>
+      </c>
+      <c r="B10" t="n">
+        <v>78977</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>750719</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7111349</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130134263</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79220</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>750665</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7111235</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130134351</v>
+      </c>
+      <c r="B12" t="n">
+        <v>93073</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4366</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skarp dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum peckii</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Banker</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>750716</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7111284</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Lussetti</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130134271</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79220</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>750620</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7111033</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130134238</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98971</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>750467</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7110939</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130134270</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79220</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>750644</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7111054</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130134258</v>
+      </c>
+      <c r="B16" t="n">
+        <v>78623</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>750733</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7111297</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130134250</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79220</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>750614</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7110958</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130134257</v>
+      </c>
+      <c r="B18" t="n">
+        <v>8440</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>750740</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7111322</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-08-29</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Lisa Sandberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130134354</v>
+      </c>
+      <c r="B19" t="n">
+        <v>93099</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>750685</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7111314</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Daniel Lussetti</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130134355</v>
+      </c>
+      <c r="B20" t="n">
+        <v>93099</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Huggberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>750714</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7111325</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Umeå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Umeå socken</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Sofia Lundman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Daniel Lussetti</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49000-2025 artfynd.xlsx
+++ b/artfynd/A 49000-2025 artfynd.xlsx
@@ -792,7 +792,7 @@
         <v>130134265</v>
       </c>
       <c r="B3" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -893,7 +893,7 @@
         <v>130134356</v>
       </c>
       <c r="B4" t="n">
-        <v>93061</v>
+        <v>93062</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>130134267</v>
       </c>
       <c r="B5" t="n">
-        <v>98971</v>
+        <v>98974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1095,7 +1095,7 @@
         <v>130134262</v>
       </c>
       <c r="B6" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>130134353</v>
       </c>
       <c r="B7" t="n">
-        <v>93061</v>
+        <v>93062</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1294,10 +1294,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130134261</v>
+        <v>130134269</v>
       </c>
       <c r="B8" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>750701</v>
+        <v>750667</v>
       </c>
       <c r="R8" t="n">
-        <v>7111370</v>
+        <v>7111133</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1395,10 +1395,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130134269</v>
+        <v>130134261</v>
       </c>
       <c r="B9" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1430,10 +1430,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>750667</v>
+        <v>750701</v>
       </c>
       <c r="R9" t="n">
-        <v>7111133</v>
+        <v>7111370</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130134260</v>
+        <v>130134263</v>
       </c>
       <c r="B10" t="n">
-        <v>78977</v>
+        <v>79221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>750719</v>
+        <v>750665</v>
       </c>
       <c r="R10" t="n">
-        <v>7111349</v>
+        <v>7111235</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130134263</v>
+        <v>130134260</v>
       </c>
       <c r="B11" t="n">
-        <v>79220</v>
+        <v>78978</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1608,21 +1608,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>750665</v>
+        <v>750719</v>
       </c>
       <c r="R11" t="n">
-        <v>7111235</v>
+        <v>7111349</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1701,7 +1701,7 @@
         <v>130134351</v>
       </c>
       <c r="B12" t="n">
-        <v>93073</v>
+        <v>93074</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1799,32 +1799,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130134271</v>
+        <v>130134238</v>
       </c>
       <c r="B13" t="n">
-        <v>79220</v>
+        <v>98974</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>750620</v>
+        <v>750467</v>
       </c>
       <c r="R13" t="n">
-        <v>7111033</v>
+        <v>7110939</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,32 +1900,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130134238</v>
+        <v>130134271</v>
       </c>
       <c r="B14" t="n">
-        <v>98971</v>
+        <v>79221</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1935,10 +1935,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>750467</v>
+        <v>750620</v>
       </c>
       <c r="R14" t="n">
-        <v>7110939</v>
+        <v>7111033</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2004,7 +2004,7 @@
         <v>130134270</v>
       </c>
       <c r="B15" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2105,7 +2105,7 @@
         <v>130134258</v>
       </c>
       <c r="B16" t="n">
-        <v>78623</v>
+        <v>78624</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>130134250</v>
       </c>
       <c r="B17" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>130134354</v>
       </c>
       <c r="B19" t="n">
-        <v>93099</v>
+        <v>93100</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>130134355</v>
       </c>
       <c r="B20" t="n">
-        <v>93099</v>
+        <v>93100</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 49000-2025 artfynd.xlsx
+++ b/artfynd/A 49000-2025 artfynd.xlsx
@@ -1294,7 +1294,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130134269</v>
+        <v>130134261</v>
       </c>
       <c r="B8" t="n">
         <v>79221</v>
@@ -1329,10 +1329,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>750667</v>
+        <v>750701</v>
       </c>
       <c r="R8" t="n">
-        <v>7111133</v>
+        <v>7111370</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1395,7 +1395,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130134261</v>
+        <v>130134269</v>
       </c>
       <c r="B9" t="n">
         <v>79221</v>
@@ -1430,10 +1430,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>750701</v>
+        <v>750667</v>
       </c>
       <c r="R9" t="n">
-        <v>7111370</v>
+        <v>7111133</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1799,32 +1799,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130134238</v>
+        <v>130134271</v>
       </c>
       <c r="B13" t="n">
-        <v>98974</v>
+        <v>79221</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1834,10 +1834,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>750467</v>
+        <v>750620</v>
       </c>
       <c r="R13" t="n">
-        <v>7110939</v>
+        <v>7111033</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,32 +1900,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130134271</v>
+        <v>130134238</v>
       </c>
       <c r="B14" t="n">
-        <v>79221</v>
+        <v>98974</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1935,10 +1935,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>750620</v>
+        <v>750467</v>
       </c>
       <c r="R14" t="n">
-        <v>7111033</v>
+        <v>7110939</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>

--- a/artfynd/A 49000-2025 artfynd.xlsx
+++ b/artfynd/A 49000-2025 artfynd.xlsx
@@ -890,32 +890,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130134356</v>
+        <v>130134267</v>
       </c>
       <c r="B4" t="n">
-        <v>93062</v>
+        <v>98974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>750732</v>
+        <v>750666</v>
       </c>
       <c r="R4" t="n">
-        <v>7111314</v>
+        <v>7111136</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,12 +955,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,7 +980,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Lussetti</t>
+          <t>Lisa Sandberg</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -991,32 +991,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130134267</v>
+        <v>130134356</v>
       </c>
       <c r="B5" t="n">
-        <v>98974</v>
+        <v>93062</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>750666</v>
+        <v>750732</v>
       </c>
       <c r="R5" t="n">
-        <v>7111136</v>
+        <v>7111314</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lisa Sandberg</t>
+          <t>Daniel Lussetti</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130134263</v>
+        <v>130134260</v>
       </c>
       <c r="B10" t="n">
-        <v>79221</v>
+        <v>78978</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>750665</v>
+        <v>750719</v>
       </c>
       <c r="R10" t="n">
-        <v>7111235</v>
+        <v>7111349</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130134260</v>
+        <v>130134263</v>
       </c>
       <c r="B11" t="n">
-        <v>78978</v>
+        <v>79221</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1608,21 +1608,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>750719</v>
+        <v>750665</v>
       </c>
       <c r="R11" t="n">
-        <v>7111349</v>
+        <v>7111235</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>

--- a/artfynd/A 49000-2025 artfynd.xlsx
+++ b/artfynd/A 49000-2025 artfynd.xlsx
@@ -890,32 +890,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130134267</v>
+        <v>130134356</v>
       </c>
       <c r="B4" t="n">
-        <v>98974</v>
+        <v>93062</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,10 +925,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>750666</v>
+        <v>750732</v>
       </c>
       <c r="R4" t="n">
-        <v>7111136</v>
+        <v>7111314</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -955,12 +955,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -980,7 +980,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lisa Sandberg</t>
+          <t>Daniel Lussetti</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -991,32 +991,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130134356</v>
+        <v>130134267</v>
       </c>
       <c r="B5" t="n">
-        <v>93062</v>
+        <v>98974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>750732</v>
+        <v>750666</v>
       </c>
       <c r="R5" t="n">
-        <v>7111314</v>
+        <v>7111136</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,12 +1056,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Lussetti</t>
+          <t>Lisa Sandberg</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">

--- a/artfynd/A 49000-2025 artfynd.xlsx
+++ b/artfynd/A 49000-2025 artfynd.xlsx
@@ -893,7 +893,7 @@
         <v>130134356</v>
       </c>
       <c r="B4" t="n">
-        <v>93062</v>
+        <v>93071</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>130134267</v>
       </c>
       <c r="B5" t="n">
-        <v>98974</v>
+        <v>98988</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
         <v>130134353</v>
       </c>
       <c r="B7" t="n">
-        <v>93062</v>
+        <v>93071</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130134260</v>
+        <v>130134263</v>
       </c>
       <c r="B10" t="n">
-        <v>78978</v>
+        <v>79221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>750719</v>
+        <v>750665</v>
       </c>
       <c r="R10" t="n">
-        <v>7111349</v>
+        <v>7111235</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130134263</v>
+        <v>130134260</v>
       </c>
       <c r="B11" t="n">
-        <v>79221</v>
+        <v>78978</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1608,21 +1608,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>750665</v>
+        <v>750719</v>
       </c>
       <c r="R11" t="n">
-        <v>7111235</v>
+        <v>7111349</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1701,7 +1701,7 @@
         <v>130134351</v>
       </c>
       <c r="B12" t="n">
-        <v>93074</v>
+        <v>93083</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1903,7 +1903,7 @@
         <v>130134238</v>
       </c>
       <c r="B14" t="n">
-        <v>98974</v>
+        <v>98988</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>130134354</v>
       </c>
       <c r="B19" t="n">
-        <v>93100</v>
+        <v>93109</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2514,7 +2514,7 @@
         <v>130134355</v>
       </c>
       <c r="B20" t="n">
-        <v>93100</v>
+        <v>93109</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 49000-2025 artfynd.xlsx
+++ b/artfynd/A 49000-2025 artfynd.xlsx
@@ -994,7 +994,7 @@
         <v>130134267</v>
       </c>
       <c r="B5" t="n">
-        <v>98988</v>
+        <v>98989</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1496,10 +1496,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130134263</v>
+        <v>130134260</v>
       </c>
       <c r="B10" t="n">
-        <v>79221</v>
+        <v>78978</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1507,21 +1507,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>750665</v>
+        <v>750719</v>
       </c>
       <c r="R10" t="n">
-        <v>7111235</v>
+        <v>7111349</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1597,10 +1597,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130134260</v>
+        <v>130134263</v>
       </c>
       <c r="B11" t="n">
-        <v>78978</v>
+        <v>79221</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1608,21 +1608,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1632,10 +1632,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>750719</v>
+        <v>750665</v>
       </c>
       <c r="R11" t="n">
-        <v>7111349</v>
+        <v>7111235</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1903,7 +1903,7 @@
         <v>130134238</v>
       </c>
       <c r="B14" t="n">
-        <v>98988</v>
+        <v>98989</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 49000-2025 artfynd.xlsx
+++ b/artfynd/A 49000-2025 artfynd.xlsx
@@ -675,52 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129574107</v>
+        <v>130134353</v>
       </c>
       <c r="B2" t="n">
-        <v>56930</v>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kälen, Vb</t>
+          <t>Huggberget, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>750675</v>
+        <v>750686</v>
       </c>
       <c r="R2" t="n">
-        <v>7111322</v>
+        <v>7111300</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -747,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>06:44</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>06:44</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,22 +760,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Elin Lindmark</t>
+          <t>Sofia Lundman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Via Elin Lindmark</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Daniel Lussetti</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Ecogain</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130134265</v>
+        <v>130134356</v>
       </c>
       <c r="B3" t="n">
-        <v>79244</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -824,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>750588</v>
+        <v>750732</v>
       </c>
       <c r="R3" t="n">
-        <v>7111098</v>
+        <v>7111314</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,7 +866,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lisa Sandberg</t>
+          <t>Daniel Lussetti</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -890,32 +877,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130134356</v>
+        <v>130134351</v>
       </c>
       <c r="B4" t="n">
-        <v>93096</v>
+        <v>93209</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -925,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>750732</v>
+        <v>750716</v>
       </c>
       <c r="R4" t="n">
-        <v>7111314</v>
+        <v>7111284</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -991,32 +978,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130134267</v>
+        <v>130134354</v>
       </c>
       <c r="B5" t="n">
-        <v>99014</v>
+        <v>93235</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>750666</v>
+        <v>750685</v>
       </c>
       <c r="R5" t="n">
-        <v>7111136</v>
+        <v>7111314</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1056,12 +1043,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,7 +1068,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lisa Sandberg</t>
+          <t>Daniel Lussetti</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1092,10 +1079,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130134262</v>
+        <v>130134355</v>
       </c>
       <c r="B6" t="n">
-        <v>79244</v>
+        <v>93235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1103,21 +1090,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1127,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>750629</v>
+        <v>750714</v>
       </c>
       <c r="R6" t="n">
-        <v>7111290</v>
+        <v>7111325</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1157,12 +1144,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1182,7 +1169,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lisa Sandberg</t>
+          <t>Daniel Lussetti</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1193,32 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130134353</v>
+        <v>130134250</v>
       </c>
       <c r="B7" t="n">
-        <v>93096</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1228,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>750686</v>
+        <v>750614</v>
       </c>
       <c r="R7" t="n">
-        <v>7111300</v>
+        <v>7110958</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1258,12 +1245,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1283,7 +1270,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Lussetti</t>
+          <t>Lisa Sandberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1294,14 +1281,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130134269</v>
+        <v>130134261</v>
       </c>
       <c r="B8" t="n">
-        <v>79244</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1329,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>750667</v>
+        <v>750701</v>
       </c>
       <c r="R8" t="n">
-        <v>7111133</v>
+        <v>7111370</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1395,14 +1382,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130134261</v>
+        <v>130134262</v>
       </c>
       <c r="B9" t="n">
-        <v>79244</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1430,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>750701</v>
+        <v>750629</v>
       </c>
       <c r="R9" t="n">
-        <v>7111370</v>
+        <v>7111290</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,11 +1486,11 @@
         <v>130134263</v>
       </c>
       <c r="B10" t="n">
-        <v>79244</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1597,32 +1584,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130134260</v>
+        <v>130134265</v>
       </c>
       <c r="B11" t="n">
-        <v>79001</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1632,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>750719</v>
+        <v>750588</v>
       </c>
       <c r="R11" t="n">
-        <v>7111349</v>
+        <v>7111098</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,32 +1685,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130134351</v>
+        <v>130134269</v>
       </c>
       <c r="B12" t="n">
-        <v>93108</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1733,10 +1720,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>750716</v>
+        <v>750667</v>
       </c>
       <c r="R12" t="n">
-        <v>7111284</v>
+        <v>7111133</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1763,12 +1750,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1788,7 +1775,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Lussetti</t>
+          <t>Lisa Sandberg</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -1799,14 +1786,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130134271</v>
+        <v>130134270</v>
       </c>
       <c r="B13" t="n">
-        <v>79244</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1834,10 +1821,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>750620</v>
+        <v>750644</v>
       </c>
       <c r="R13" t="n">
-        <v>7111033</v>
+        <v>7111054</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1900,10 +1887,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130134238</v>
+        <v>130134271</v>
       </c>
       <c r="B14" t="n">
-        <v>99014</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1911,21 +1898,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1935,10 +1922,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>750467</v>
+        <v>750620</v>
       </c>
       <c r="R14" t="n">
-        <v>7110939</v>
+        <v>7111033</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,10 +1988,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130134270</v>
+        <v>130134258</v>
       </c>
       <c r="B15" t="n">
-        <v>79244</v>
+        <v>78730</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2012,21 +1999,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6437</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2036,10 +2023,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>750644</v>
+        <v>750733</v>
       </c>
       <c r="R15" t="n">
-        <v>7111054</v>
+        <v>7111297</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2102,10 +2089,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130134258</v>
+        <v>130134260</v>
       </c>
       <c r="B16" t="n">
-        <v>78647</v>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2113,21 +2100,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6437</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2137,10 +2124,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>750733</v>
+        <v>750719</v>
       </c>
       <c r="R16" t="n">
-        <v>7111297</v>
+        <v>7111349</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2203,45 +2190,52 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130134250</v>
+        <v>129574107</v>
       </c>
       <c r="B17" t="n">
-        <v>79244</v>
+        <v>57141</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Huggberget, Vb</t>
+          <t>Kälen, Vb</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>750614</v>
+        <v>750675</v>
       </c>
       <c r="R17" t="n">
-        <v>7110958</v>
+        <v>7111322</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2268,12 +2262,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>06:44</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-08-29</t>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>06:44</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2288,26 +2292,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Sofia Lundman</t>
+          <t>Elin Lindmark</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Lisa Sandberg</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>Ecogain</t>
-        </is>
-      </c>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>130134257</v>
       </c>
       <c r="B18" t="n">
-        <v>8440</v>
+        <v>8444</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2410,32 +2410,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130134354</v>
+        <v>130134238</v>
       </c>
       <c r="B19" t="n">
-        <v>93134</v>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2445,10 +2445,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>750685</v>
+        <v>750467</v>
       </c>
       <c r="R19" t="n">
-        <v>7111314</v>
+        <v>7110939</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2475,12 +2475,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Lussetti</t>
+          <t>Lisa Sandberg</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
@@ -2511,32 +2511,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130134355</v>
+        <v>130134267</v>
       </c>
       <c r="B20" t="n">
-        <v>93134</v>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5966</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2546,10 +2546,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>750714</v>
+        <v>750666</v>
       </c>
       <c r="R20" t="n">
-        <v>7111325</v>
+        <v>7111136</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2576,12 +2576,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-08-29</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Lussetti</t>
+          <t>Lisa Sandberg</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">

--- a/artfynd/A 49000-2025 artfynd.xlsx
+++ b/artfynd/A 49000-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130134250</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130134265</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130134269</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130134270</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130134271</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130134238</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130134267</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130134353</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130134356</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1682,6 +1732,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130134351</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1783,6 +1838,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130134354</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1884,6 +1944,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130134355</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1985,6 +2050,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130134261</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2086,6 +2156,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130134262</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2187,6 +2262,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130134263</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2288,6 +2368,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130134258</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2389,6 +2474,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130134260</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2503,6 +2593,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129574107</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2609,8 +2704,34 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130134257</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>